--- a/uploads/input_corretto.xlsx
+++ b/uploads/input_corretto.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1, Via di Sant'Antonio, Cusiano, Ossana, Comunità della Valle di Sole, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38027, Italia</t>
+          <t>Via di Sant'Antonio, 1, 38027 Ossana TN</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Piazza Fiera, Dres, Cles, Comunità della Val di Non, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38028, Italia</t>
+          <t>Piazza Fiera, 38028 Cles TN</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -489,7 +489,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liceo Bertrand Russell, 35, Via Quattro Novembre, Dres, Cles, Comunità della Val di Non, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38023, Italia</t>
+          <t>Via Quattro Novembre, 35, 38023 Cles TN</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mezzolombardo Stazione FTM, Via San Francesco, Mezzolombardo, Comunità Rotaliana-Königsberg, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38016, Italia</t>
+          <t>Via San Francesco, 38016 Mezzolombardo TN</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -527,7 +527,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fiera di Primiero, Transacqua, Primiero San Martino di Castrozza, Comunità di Primiero, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38054, Italia</t>
+          <t>Fiera di Primiero, 38054 Primiero San Martino di Castrozza TN</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fiera di Primiero, Transacqua, Primiero San Martino di Castrozza, Comunità di Primiero, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38054, Italia</t>
+          <t>Fiera di Primiero, 38054 Primiero San Martino di Castrozza TN</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Via Hippoliti, Olle, Borgo Valsugana, Comunità Valsugana e Tesino, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38051, Italia</t>
+          <t>Via Hippoliti, 16, 38051 Borgo Valsugana TN</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -584,7 +584,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liceo Fabio Filzi, 61, Corso Antonio Rosmini, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
+          <t>Corso Antonio Rosmini, 61, 38068 Rovereto TN</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liceo Fabio Filzi, 61, Corso Antonio Rosmini, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
+          <t>Corso Antonio Rosmini, 61, 38068 Rovereto TN</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Strada Dolomites, Sèn Jan, Pozza di Fassa - Poza, San Giovanni di Fassa - Sèn Jan, Comun General de Fascia, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38036, Italia</t>
+          <t>Strada Dolomites, 38036 San Giovanni di Fassa TN</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Piazza Giuseppe Verdi, Cavalese, Comunità territoriale della Val di Fiemme, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38099, Italia</t>
+          <t>Piazza Giuseppe Verdi, 6, 38099 Cavalese TN</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Caltrezza, Tesero, Comunità territoriale della Val di Fiemme, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38099, Italia</t>
+          <t>Via Caltrezza, 13, 38038 Tesero TN</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>84, Corso Bettini, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
+          <t>Corso Bettini, 84, 38068 Rovereto TN</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -698,7 +698,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Palazzo Fedrigotti, 31, Corso Bettini, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
+          <t>Corso Bettini, 31, 38068 Rovereto TN</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -717,7 +717,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liceo Scientifico "Leonardo da Vinci", 24, Via Cardinale Cristoforo Madruzzo, Le Albere, San Giuseppe - Santa Chiara, Sardagna, Trento, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 31822, Italia</t>
+          <t>Via Cardinale Cristoforo Madruzzo, 24, 38122 Trento TN</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Via Luigi Negrelli, San Giacomo, Riva del Garda, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38066, Italia</t>
+          <t>Via Luigi Negrelli, 11, 38066 Riva del Garda TN</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scuole superiori Gardascuola, 1, Via Ventiquattro Maggio, Caneve, Chiarano, Arco, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38062, Italia</t>
+          <t>Via Ventiquattro Maggio, 1, 38062 Arco TN</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Piazza Gavazzi, Fontanabotte, Susà, Pergine Valsugana, Comunità Alta Valsugana e Bersntol, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38057, Italia</t>
+          <t>Piazza Gavazzi, 1, 38057 Pergine Valsugana TN</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Istituto di istruzione "Lorenzo Guetti", 53, Via Durone, Basso Arnò, Tione di Trento, Comunità delle Giudicarie, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38079, Italia</t>
+          <t>Via Durone, 53, 38079 Tione di Trento TN</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Centro Formazione Professionale ENAIP - Tione di Trento, 57, Via Durone, Basso Arnò, Tione di Trento, Comunità delle Giudicarie, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38079, Italia</t>
+          <t>Via Durone, 57, 38079 Tione di Trento TN</t>
         </is>
       </c>
       <c r="C21" t="n">
